--- a/Bibsam_tidskriftslistor/scifree_data_iwa.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_iwa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F6713C95BC6D6C505186E45C34475E95226B6AFF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77AF093A-2152-4ADA-B3EE-3090CC2C74A2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C529D31A-9046-4C1C-AD47-F6BFD6A13A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
   <si>
     <t>Open</t>
   </si>
@@ -55,12 +55,6 @@
     <t>Blue-Green Systems</t>
   </si>
   <si>
-    <t>H2Open Journal</t>
-  </si>
-  <si>
-    <t>Hydrology Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Journal of Hydroinformatics </t>
   </si>
   <si>
@@ -100,15 +94,6 @@
     <t>2617-4782</t>
   </si>
   <si>
-    <t>2616-6518</t>
-  </si>
-  <si>
-    <t>0029-1277</t>
-  </si>
-  <si>
-    <t>2224-7955</t>
-  </si>
-  <si>
     <t>1464-7141</t>
   </si>
   <si>
@@ -170,12 +155,6 @@
   </si>
   <si>
     <t>https://iwaponline.com/bgs</t>
-  </si>
-  <si>
-    <t>https://iwaponline.com/h2open</t>
-  </si>
-  <si>
-    <t>https://iwaponline.com/hr</t>
   </si>
   <si>
     <t>https://iwaponline.com/jh</t>
@@ -224,26 +203,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -266,70 +229,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -343,19 +252,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G16" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:G16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
-    <sortCondition ref="D1:D8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{456DF2DD-EDC8-420F-BA09-1D3E1E609A25}" name="Table2" displayName="Table2" ref="A1:G14" totalsRowShown="0">
+  <autoFilter ref="A1:G14" xr:uid="{456DF2DD-EDC8-420F-BA09-1D3E1E609A25}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
+    <sortCondition ref="D1:D14"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{F4FBA26F-37E4-4296-B737-FEC1C68545A0}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{1B14DA0F-5A81-49EE-9F72-A13C3A1E5BAD}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{ECF0345E-AD86-42D4-ADE5-B580CA677E65}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{13D2254A-36A7-4024-B717-52513A9F097E}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{FA42550E-F6C0-4B5B-969D-F75FE2FF297A}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{1ECFAB60-0D71-4F97-81D7-89BCB6DE7717}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{39A7C2D7-EA00-4D83-A324-27083583039E}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -623,57 +532,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D647DC-57C6-4143-AEE8-74E0FD055F24}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="49.5703125" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
@@ -684,16 +593,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
         <v>0</v>
@@ -704,16 +613,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
@@ -724,19 +636,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -747,19 +659,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
@@ -770,19 +682,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -793,19 +705,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>0</v>
@@ -816,19 +728,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -839,19 +751,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>0</v>
@@ -862,19 +774,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -885,19 +797,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
         <v>0</v>
@@ -908,16 +817,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -928,19 +840,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
@@ -949,69 +861,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D24" s="2"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D23 D25:D1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E16">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>